--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_fewshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_fewshot.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -39960,7 +39960,7 @@
       </c>
       <c r="C2325" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -48443,7 +48443,7 @@
       </c>
       <c r="C2824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6494192185850053</v>
+        <v>0.6356916578669483</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5380379203742668</v>
+        <v>0.5097380137423113</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5729294094911792</v>
+        <v>0.5479614460218019</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7729639180138494</v>
+        <v>0.7669526664358888</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5877977927777479</v>
+        <v>0.5712421031045471</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>794.593716069</v>
+        <v>1700.138291798998</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2796880380390708</v>
+        <v>0.5984295289683202</v>
       </c>
     </row>
   </sheetData>
